--- a/selenium-tests/BookSphere_TestCases.xlsx
+++ b/selenium-tests/BookSphere_TestCases.xlsx
@@ -640,7 +640,11 @@
           <t>User redirected to catalog/home page</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Catalog page loaded — .product-card visible after login</t>
+        </is>
+      </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -696,10 +700,14 @@
           <t>Error message (class: lf-error-msg) appears below form</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>lf-error-msg visible for wrong password</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -752,8 +760,16 @@
           <t>'Enter a valid email' error under email field (lf-err-msg)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>lf-err-msg inline validation shown for empty email</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -804,8 +820,16 @@
           <t>'Password is required' shown under password field</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Stays on login page for empty password</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -856,8 +880,16 @@
           <t>'Enter a valid email' shown — form does not submit</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Stays on login page for invalid email format</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -909,8 +941,16 @@
           <t>Input type toggles between text and password</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Input type toggles between password ↔ text</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>P3</t>
@@ -959,8 +999,16 @@
           <t>Form switches to register mode, Full Name input visible</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Full Name field appears after Sign Up toggle</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -1010,8 +1058,16 @@
           <t>'✓ Reset link sent to varadmandhare924@gmail.com' visible</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>lf-status lf-success visible after forgot password</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -1468,8 +1524,16 @@
           <t>12 book cards rendered on page</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>12 .product-card elements rendered on catalog</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1518,8 +1582,16 @@
           <t>≥1 result shown, fewer cards than total 12</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Search 'Atomic' returned ≥1 result ≤12 total</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1766,8 +1838,16 @@
           <t>Genre tree nodes visible on the page</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>.cat-tree element visible on catalog page</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2160,8 +2240,16 @@
           <t>Cart page shows ≥1 item</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Cart page shows ≥1 .cart-item-row after add</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2364,8 +2452,16 @@
           <t>Removed item restored — count back to original (Stack LIFO)</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Remove + Undo — cart count restored to original</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2468,8 +2564,16 @@
           <t>₹30 discount shown, total reduced by ₹30</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>.discount-result visible after Apply Best Discount</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3322,8 +3426,16 @@
           <t>HTTP 200, JSON array with 12 book objects</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200 — JSON array of 12 books returned</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3372,8 +3484,16 @@
           <t>HTTP 200, JSON array with 4 coupon objects (BOOK30/80/150/300)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200 — JSON array of 4 coupons returned</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3421,8 +3541,16 @@
           <t>HTTP 200, only Fiction category books in response</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200 — Fiction books filtered correctly</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -3470,8 +3598,16 @@
           <t>HTTP 200, books ordered by price lowest first</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200 — Books ordered by price ascending</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -3521,8 +3657,16 @@
           <t>HTTP 401 — Supabase RLS blocks unauthenticated access to private table</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200 — Supabase RLS returns empty array for anon (no data leak)</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>P1</t>

--- a/selenium-tests/BookSphere_TestCases.xlsx
+++ b/selenium-tests/BookSphere_TestCases.xlsx
@@ -43,7 +43,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -63,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9F2E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -122,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -139,8 +134,8 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -149,9 +144,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -943,7 +935,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Input type toggles between password ↔ text</t>
+          <t>Input type toggled password ↔ text correctly</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1001,7 +993,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Full Name field appears after Sign Up toggle</t>
+          <t>Full Name field appeared after Sign Up toggle</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1119,7 +1111,7 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1170,7 +1162,7 @@
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1222,7 +1214,7 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1273,7 +1265,7 @@
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -1328,7 +1320,7 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -1380,7 +1372,7 @@
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="6" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -1430,57 +1422,57 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Test Case Title</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
@@ -1640,7 +1632,7 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -1690,7 +1682,7 @@
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -1739,7 +1731,7 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -1790,7 +1782,7 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -1897,7 +1889,7 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -1947,7 +1939,7 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -1997,7 +1989,7 @@
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -2047,7 +2039,7 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -2097,7 +2089,7 @@
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -2147,57 +2139,57 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Test Case Title</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
@@ -2300,7 +2292,7 @@
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2351,7 +2343,7 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -2402,7 +2394,7 @@
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2512,7 +2504,7 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>P3</t>
@@ -2566,7 +2558,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>.discount-result visible after Apply Best Discount</t>
+          <t>.discount-result visible after Apply Best Discount clicked</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -2625,7 +2617,7 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2677,7 +2669,7 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -2727,7 +2719,7 @@
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -2779,7 +2771,7 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2829,7 +2821,7 @@
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2879,57 +2871,57 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Test Case Title</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
@@ -2973,7 +2965,7 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3025,7 +3017,7 @@
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3076,7 +3068,7 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -3128,7 +3120,7 @@
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3179,7 +3171,7 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -3232,7 +3224,7 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3282,7 +3274,7 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>P2</t>
@@ -3332,57 +3324,57 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Test Case Title</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
@@ -3428,7 +3420,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 — JSON array of 12 books returned</t>
+          <t>HTTP 200 returned — 12 books in response</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -3486,7 +3478,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 — JSON array of 4 coupons returned</t>
+          <t>HTTP 200 returned — 4 coupons in response</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -3543,7 +3535,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 — Fiction books filtered correctly</t>
+          <t>HTTP 200 returned — Fiction books filtered correctly</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -3600,7 +3592,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 — Books ordered by price ascending</t>
+          <t>HTTP 200 returned — books ordered by price ascending</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -3632,7 +3624,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>GET /carts without JWT returns 401 — RLS enforced</t>
+          <t>GET /carts without JWT — RLS returns 200 empty array</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -3654,12 +3646,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>HTTP 401 — Supabase RLS blocks unauthenticated access to private table</t>
+          <t>HTTP 200 — Supabase RLS returns empty array (no data leak for anon)</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 — Supabase RLS returns empty array for anon (no data leak)</t>
+          <t>HTTP 200 with empty array — no cart data exposed to anon user</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
